--- a/data/trans_camb/P57_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P57_R-Provincia-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,32; -18,02</t>
+          <t>-30,65; -18,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-30,89; -18,77</t>
+          <t>-30,81; -19,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,69; -19,73</t>
+          <t>-28,44; -20,09</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-87,99; -67,44</t>
+          <t>-88,31; -70,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-86,21; -71,07</t>
+          <t>-86,03; -70,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,13; -72,33</t>
+          <t>-85,12; -71,98</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,89; -4,84</t>
+          <t>-12,67; -4,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,53; -4,95</t>
+          <t>-12,31; -5,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,52; -6,01</t>
+          <t>-11,53; -6,23</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,14; -34,44</t>
+          <t>-77,27; -35,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,62; -39,37</t>
+          <t>-71,09; -39,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,08; -45,11</t>
+          <t>-70,98; -47,05</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,93; 16,07</t>
+          <t>5,89; 16,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 10,56</t>
+          <t>-0,52; 10,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 11,66</t>
+          <t>4,28; 11,65</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55,95; 264,13</t>
+          <t>47,91; 253,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 84,38</t>
+          <t>-3,14; 85,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30,82; 115,13</t>
+          <t>31,14; 116,48</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 2,09</t>
+          <t>-8,55; 3,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-24,96; -12,08</t>
+          <t>-24,97; -12,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,49; -7,06</t>
+          <t>-15,56; -6,97</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,47; 17,0</t>
+          <t>-46,37; 23,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-78,99; -47,93</t>
+          <t>-79,22; -49,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,53; -34,79</t>
+          <t>-65,23; -34,23</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-34,21; -20,46</t>
+          <t>-34,2; -20,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-39,9; -26,26</t>
+          <t>-39,23; -25,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-34,97; -25,08</t>
+          <t>-34,91; -24,63</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-86,65; -68,24</t>
+          <t>-87,38; -67,5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-84,65; -71,04</t>
+          <t>-84,44; -71,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,47; -71,6</t>
+          <t>-83,49; -72,28</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 8,49</t>
+          <t>-4,62; 8,92</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 7,04</t>
+          <t>-5,43; 7,18</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 6,47</t>
+          <t>-3,39; 6,02</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 56,83</t>
+          <t>-20,32; 60,88</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-23,23; 39,61</t>
+          <t>-21,42; 41,03</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 37,72</t>
+          <t>-14,9; 34,36</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-11,13; -3,44</t>
+          <t>-10,85; -3,17</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-18,22; -6,28</t>
+          <t>-18,48; -6,37</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,06; -6,2</t>
+          <t>-13,25; -5,87</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-59,46; -23,27</t>
+          <t>-58,7; -21,89</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-82,24; -32,62</t>
+          <t>-77,39; -32,38</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-67,23; -35,85</t>
+          <t>-67,81; -34,57</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 4,26</t>
+          <t>-14,1; 4,54</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4,37; 12,79</t>
+          <t>4,08; 12,92</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 6,8</t>
+          <t>-8,75; 6,85</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-65,83; 22,57</t>
+          <t>-62,51; 23,77</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>15,73; 55,8</t>
+          <t>14,7; 56,37</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-36,78; 30,67</t>
+          <t>-37,54; 30,83</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-8,62; -3,84</t>
+          <t>-9,03; -4,03</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -5,58</t>
+          <t>-10,83; -5,58</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,88; -5,31</t>
+          <t>-9,06; -5,46</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-45,62; -22,16</t>
+          <t>-47,72; -22,9</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-44,5; -25,08</t>
+          <t>-45,26; -24,65</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-41,48; -26,16</t>
+          <t>-41,21; -26,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P57_R-Provincia-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-24,04</t>
+          <t>-24,28</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-24,58</t>
+          <t>-24,65</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-24,32</t>
+          <t>-24,46</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,65; -18,26</t>
+          <t>-30,24; -18,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-30,81; -19,35</t>
+          <t>-30,6; -18,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,44; -20,09</t>
+          <t>-28,73; -20,81</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-80,49%</t>
+          <t>-81,3%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-79,14%</t>
+          <t>-79,38%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-79,84%</t>
+          <t>-80,32%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-88,31; -70,32</t>
+          <t>-88,96; -70,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-86,03; -70,95</t>
+          <t>-85,63; -69,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,12; -71,98</t>
+          <t>-85,25; -74,41</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-8,92</t>
+          <t>-8,88</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-8,72</t>
+          <t>-8,81</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-8,83</t>
+          <t>-8,85</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,67; -4,45</t>
+          <t>-12,66; -5,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,31; -5,03</t>
+          <t>-12,53; -5,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,53; -6,23</t>
+          <t>-11,53; -5,8</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-61,94%</t>
+          <t>-61,67%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-58,83%</t>
+          <t>-59,44%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-60,39%</t>
+          <t>-60,53%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,27; -35,8</t>
+          <t>-76,91; -37,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-71,09; -39,47</t>
+          <t>-71,29; -41,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,98; -47,05</t>
+          <t>-70,43; -44,44</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11,09</t>
+          <t>11,9</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>4,91</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,15</t>
+          <t>8,31</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,89; 16,42</t>
+          <t>6,84; 17,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 10,68</t>
+          <t>-0,3; 9,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 11,65</t>
+          <t>4,41; 12,06</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>131,05%</t>
+          <t>140,59%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>68,82%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47,91; 253,17</t>
+          <t>61,91; 267,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 85,13</t>
+          <t>-2,19; 80,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31,14; 116,48</t>
+          <t>29,42; 120,1</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-3,26</t>
+          <t>-3,99</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-17,91</t>
+          <t>-15,48</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-10,99</t>
+          <t>-9,86</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 3,2</t>
+          <t>-9,68; 1,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-24,97; -12,34</t>
+          <t>-21,17; -9,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,56; -6,97</t>
+          <t>-14,13; -6,12</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-20,56%</t>
+          <t>-25,17%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-63,94%</t>
+          <t>-55,28%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-49,76%</t>
+          <t>-44,67%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 23,65</t>
+          <t>-52,82; 8,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-79,22; -49,03</t>
+          <t>-66,96; -39,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,23; -34,23</t>
+          <t>-56,65; -29,95</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-27,15</t>
+          <t>-27,28</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-32,6</t>
+          <t>-32,9</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-29,87</t>
+          <t>-30,11</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-34,2; -20,27</t>
+          <t>-34,5; -20,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-39,23; -25,45</t>
+          <t>-39,57; -25,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-34,91; -24,63</t>
+          <t>-35,05; -25,11</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-79,08%</t>
+          <t>-79,46%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-78,53%</t>
+          <t>-79,25%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-78,65%</t>
+          <t>-79,28%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-87,38; -67,5</t>
+          <t>-87,6; -67,98</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-84,44; -71,06</t>
+          <t>-84,85; -70,85</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,49; -72,28</t>
+          <t>-83,92; -72,92</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>3,7</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>2,51</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 8,92</t>
+          <t>-2,83; 9,76</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 7,18</t>
+          <t>-5,45; 7,47</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 6,02</t>
+          <t>-1,98; 6,82</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 60,88</t>
+          <t>-13,23; 66,31</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 41,03</t>
+          <t>-21,67; 43,56</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 34,36</t>
+          <t>-8,57; 39,79</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-7,12</t>
+          <t>-6,88</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-11,01</t>
+          <t>-7,56</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-9,07</t>
+          <t>-7,21</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,85; -3,17</t>
+          <t>-10,49; -3,14</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-18,48; -6,37</t>
+          <t>-11,13; -3,58</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,25; -5,87</t>
+          <t>-10,12; -4,59</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-43,57%</t>
+          <t>-42,1%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-53,01%</t>
+          <t>-36,41%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-48,78%</t>
+          <t>-38,74%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-58,7; -21,89</t>
+          <t>-55,65; -19,38</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-77,39; -32,38</t>
+          <t>-48,74; -19,34</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-67,81; -34,57</t>
+          <t>-49,76; -26,55</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-2,98</t>
+          <t>2,12</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>8,79</t>
+          <t>8,72</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,69</t>
+          <t>5,46</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 4,54</t>
+          <t>-1,81; 6,9</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4,08; 12,92</t>
+          <t>4,19; 13,14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 6,85</t>
+          <t>2,61; 8,44</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-15,1%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-62,51; 23,77</t>
+          <t>-8,69; 37,29</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>14,7; 56,37</t>
+          <t>14,99; 57,82</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-37,54; 30,83</t>
+          <t>10,71; 39,83</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-6,06</t>
+          <t>-5,12</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-7,7</t>
+          <t>-6,18</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-6,89</t>
+          <t>-5,65</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-9,03; -4,03</t>
+          <t>-7,0; -3,31</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-10,83; -5,58</t>
+          <t>-8,11; -4,28</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-9,06; -5,46</t>
+          <t>-6,9; -4,46</t>
         </is>
       </c>
     </row>
@@ -1362,17 +1362,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-32,71%</t>
+          <t>-27,66%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-32,82%</t>
+          <t>-26,32%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-32,73%</t>
+          <t>-26,85%</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-47,72; -22,9</t>
+          <t>-35,2; -18,41</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-45,26; -24,65</t>
+          <t>-33,17; -19,49</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-41,21; -26,63</t>
+          <t>-32,08; -21,9</t>
         </is>
       </c>
     </row>
